--- a/output/results_2024.xlsx
+++ b/output/results_2024.xlsx
@@ -751,7 +751,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ministero del Lavoro</t>
+          <t>Ministero del Lavoro e delle Politiche Sociali</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ministero dell'Economia e delle Finanze, Dipartimento del Tesoro</t>
+          <t>Dipartimento del Tesoro (MEF)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ministero dell'Economia e delle Finanze, Dipartimento del Tesoro</t>
+          <t>Dipartimento del Tesoro (MEF)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3887,7 +3887,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Ministero dell'Economia e delle Finanze, Dipartimento del Tesoro</t>
+          <t>Dipartimento del Tesoro (MEF)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6223,7 +6223,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Ministero dell'Istruzione</t>
+          <t>Ministero dell'Istruzione, dell'Università e della Ricerca</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6511,7 +6511,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Ministero dell'Istruzione</t>
+          <t>Ministero dell'Istruzione, dell'Università e della Ricerca</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6735,7 +6735,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ISEE Universitario | Università di Genova</t>
+          <t>Università di Genova</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7311,7 +7311,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Ministero del Lavoro</t>
+          <t>Ministero del Lavoro e delle Politiche Sociali</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -10479,7 +10479,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Ministero dell'Istruzione</t>
+          <t>Ministero dell'Istruzione, dell'Università e della Ricerca</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -10831,7 +10831,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ISEE Universitario | Università di Genova</t>
+          <t>Università di Genova</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
